--- a/mainWidget/mainWidget/src/database/壳体金属材料.xlsx
+++ b/mainWidget/mainWidget/src/database/壳体金属材料.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="151">
   <si>
     <r>
       <rPr>
@@ -1577,6 +1577,88 @@
   </si>
   <si>
     <t>5700</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D406</t>
+  </si>
+  <si>
+    <t>D406A</t>
+  </si>
+  <si>
+    <t>30CrMnSiA</t>
+  </si>
+  <si>
+    <t>钛合金TC4</t>
+  </si>
+  <si>
+    <t>铝合金7075</t>
+  </si>
+  <si>
+    <t>铝合金2A6</t>
+  </si>
+  <si>
+    <t>206000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>207000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>103000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>71700</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000118</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000115</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000086</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000234</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000023</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>31050</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30900</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10755</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15450</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10500</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1584,7 +1666,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1637,6 +1719,13 @@
       <name val="Times New Roman"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1714,10 +1803,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1759,18 +1849,19 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2063,12 +2154,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="4" max="4" width="11.3046875" style="13" customWidth="1"/>
-    <col min="5" max="6" width="18.07421875" style="13" customWidth="1"/>
-    <col min="7" max="11" width="9.23046875" style="13"/>
+    <col min="2" max="2" width="35.07421875" customWidth="1"/>
+    <col min="3" max="3" width="26.3828125" customWidth="1"/>
+    <col min="4" max="4" width="25.61328125" style="13" customWidth="1"/>
+    <col min="5" max="5" width="26.07421875" style="13" customWidth="1"/>
+    <col min="6" max="6" width="25.53515625" style="13" customWidth="1"/>
+    <col min="7" max="7" width="25.69140625" style="13" customWidth="1"/>
+    <col min="8" max="8" width="23.765625" style="13" customWidth="1"/>
+    <col min="9" max="9" width="21.3046875" style="13" customWidth="1"/>
+    <col min="10" max="10" width="19.921875" style="13" customWidth="1"/>
+    <col min="11" max="11" width="18.921875" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.45" thickBot="1" x14ac:dyDescent="0.45">
@@ -2106,7 +2204,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="31.3" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" ht="15.9" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -2141,7 +2239,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="46.75" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" ht="15.9" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -2176,7 +2274,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="31.3" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" ht="15.9" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -2211,7 +2309,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="93.9" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -2246,7 +2344,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="93.9" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -2281,7 +2379,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="78.45" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -2316,7 +2414,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="78.45" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -2351,7 +2449,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="63" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -2386,7 +2484,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="63" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -2421,7 +2519,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="47.15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -2456,7 +2554,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="62.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -2491,7 +2589,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="77.599999999999994" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -2526,7 +2624,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="78.45" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -2561,7 +2659,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="78.45" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -2596,7 +2694,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="78.45" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -2631,7 +2729,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="47.15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -2666,7 +2764,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="63" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -2701,7 +2799,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="63" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -2736,7 +2834,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="63" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -2771,7 +2869,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="63" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -2806,7 +2904,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -2841,7 +2939,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="93" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:11" ht="32.15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -2876,7 +2974,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="47.15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -2911,7 +3009,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -2946,7 +3044,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="77.599999999999994" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -2981,7 +3079,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="77.599999999999994" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -3016,7 +3114,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="93" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:11" ht="32.15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -3051,7 +3149,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="92.15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -3086,7 +3184,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="92.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:11" ht="16.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -3119,6 +3217,216 @@
       </c>
       <c r="K30" s="12">
         <v>460</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" s="5" customFormat="1" ht="15.9" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="5">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C31" s="5">
+        <v>7850</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="G31" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="H31" s="5">
+        <v>440</v>
+      </c>
+      <c r="I31" s="5">
+        <v>590</v>
+      </c>
+      <c r="J31" s="5">
+        <v>48</v>
+      </c>
+      <c r="K31" s="5">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" s="5" customFormat="1" ht="15.9" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="5">
+        <v>31</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C32" s="5">
+        <v>7850</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="G32" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="H32" s="5">
+        <v>540</v>
+      </c>
+      <c r="I32" s="5">
+        <v>690</v>
+      </c>
+      <c r="J32" s="5">
+        <v>47.5</v>
+      </c>
+      <c r="K32" s="5">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" s="5" customFormat="1" ht="15.9" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="5">
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C33" s="5">
+        <v>7850</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="G33" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="H33" s="5">
+        <v>880</v>
+      </c>
+      <c r="I33" s="5">
+        <v>1080</v>
+      </c>
+      <c r="J33" s="5">
+        <v>41</v>
+      </c>
+      <c r="K33" s="5">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" s="5" customFormat="1" ht="15.9" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="5">
+        <v>33</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C34" s="5">
+        <v>4430</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="G34" s="5">
+        <v>0.34</v>
+      </c>
+      <c r="H34" s="5">
+        <v>827</v>
+      </c>
+      <c r="I34" s="5">
+        <v>896</v>
+      </c>
+      <c r="J34" s="5">
+        <v>6.7</v>
+      </c>
+      <c r="K34" s="5">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" s="5" customFormat="1" ht="15.9" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="5">
+        <v>34</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C35" s="5">
+        <v>2810</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="G35" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="H35" s="5">
+        <v>503</v>
+      </c>
+      <c r="I35" s="5">
+        <v>572</v>
+      </c>
+      <c r="J35" s="5">
+        <v>130</v>
+      </c>
+      <c r="K35" s="5">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" s="5" customFormat="1" ht="15.9" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="5">
+        <v>35</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C36" s="5">
+        <v>2780</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="G36" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="H36" s="5">
+        <v>345</v>
+      </c>
+      <c r="I36" s="5">
+        <v>420</v>
+      </c>
+      <c r="J36" s="5">
+        <v>148</v>
+      </c>
+      <c r="K36" s="5">
+        <v>890</v>
       </c>
     </row>
   </sheetData>
